--- a/backend/database/NCC- IPM Team - Test-Tickets/Enterprise_Ticket_Tracker_With_Resolutions.xlsx
+++ b/backend/database/NCC- IPM Team - Test-Tickets/Enterprise_Ticket_Tracker_With_Resolutions.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://infics.sharepoint.com/sites/NCC-IPMTeam/TestTickets/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_E0CD2808256BF1754DE79259343A4D76B29BF10F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="19416" windowHeight="11496"/>
   </bookViews>
   <sheets>
     <sheet name="Incidents" sheetId="1" r:id="rId1"/>
@@ -24,7 +18,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">People!$A$1:$G$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">SLA_Matrix!$A$1:$D$5</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="144525"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -45,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1147" uniqueCount="492">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1167" uniqueCount="497">
   <si>
     <t>Incident_Number</t>
   </si>
@@ -248,9 +242,6 @@
     <t>2026-02-22 01:00</t>
   </si>
   <si>
-    <t>Code refactored to eliminate concurrency issue. Root cause: Database connection timeout.</t>
-  </si>
-  <si>
     <t>Database connection timeout</t>
   </si>
   <si>
@@ -350,9 +341,6 @@
     <t>2026-02-12 14:00</t>
   </si>
   <si>
-    <t>Infrastructure scaling applied and stabilized. Root cause: Incorrect role permission mapping.</t>
-  </si>
-  <si>
     <t>Incorrect role permission mapping</t>
   </si>
   <si>
@@ -395,9 +383,6 @@
     <t>2026-02-23 08:00</t>
   </si>
   <si>
-    <t>Role mapping corrected and access verified. Root cause: Memory leak in background worker.</t>
-  </si>
-  <si>
     <t>Memory leak in background worker</t>
   </si>
   <si>
@@ -431,9 +416,6 @@
     <t>2026-02-06 21:00</t>
   </si>
   <si>
-    <t>Role mapping corrected and access verified. Root cause: Expired SSL certificate.</t>
-  </si>
-  <si>
     <t>Expired SSL certificate</t>
   </si>
   <si>
@@ -470,9 +452,6 @@
     <t>2026-02-22 07:00</t>
   </si>
   <si>
-    <t>Patch deployed to production and validated by QA. Root cause: Deployment configuration mismatch.</t>
-  </si>
-  <si>
     <t>Deployment configuration mismatch</t>
   </si>
   <si>
@@ -506,9 +485,6 @@
     <t>2026-03-02 05:00</t>
   </si>
   <si>
-    <t>Issue investigated and fixed after identifying root cause. Root cause: Kafka consumer lag spike.</t>
-  </si>
-  <si>
     <t>Kafka consumer lag spike</t>
   </si>
   <si>
@@ -536,9 +512,6 @@
     <t>2026-02-08 12:00</t>
   </si>
   <si>
-    <t>Optimized query and added proper indexing. Root cause: Redis cache eviction issue.</t>
-  </si>
-  <si>
     <t>Redis cache eviction issue</t>
   </si>
   <si>
@@ -566,9 +539,6 @@
     <t>2026-02-15 13:00</t>
   </si>
   <si>
-    <t>Infrastructure scaling applied and stabilized. Root cause: Index missing on Orders table.</t>
-  </si>
-  <si>
     <t>Index missing on Orders table</t>
   </si>
   <si>
@@ -605,9 +575,6 @@
     <t>2026-03-01 11:00</t>
   </si>
   <si>
-    <t>Role mapping corrected and access verified. Root cause: Payment gateway timeout.</t>
-  </si>
-  <si>
     <t>Payment gateway timeout</t>
   </si>
   <si>
@@ -635,9 +602,6 @@
     <t>2026-02-14 11:00</t>
   </si>
   <si>
-    <t>Memory optimization applied and load tested. Root cause: File upload size limit exceeded.</t>
-  </si>
-  <si>
     <t>File upload size limit exceeded</t>
   </si>
   <si>
@@ -674,9 +638,6 @@
     <t>2026-02-09 14:00</t>
   </si>
   <si>
-    <t>Role mapping corrected and access verified. Root cause: Race condition in async handler.</t>
-  </si>
-  <si>
     <t>Race condition in async handler</t>
   </si>
   <si>
@@ -701,9 +662,6 @@
     <t>2026-02-22 02:00</t>
   </si>
   <si>
-    <t>Code refactored to eliminate concurrency issue. Root cause: JWT token expiration mismatch.</t>
-  </si>
-  <si>
     <t>JWT token expiration mismatch</t>
   </si>
   <si>
@@ -737,9 +695,6 @@
     <t>2026-02-05 03:00</t>
   </si>
   <si>
-    <t>Memory optimization applied and load tested. Root cause: Incorrect environment variable value.</t>
-  </si>
-  <si>
     <t>Incorrect environment variable value</t>
   </si>
   <si>
@@ -770,9 +725,6 @@
     <t>2026-02-19 11:00</t>
   </si>
   <si>
-    <t>Role mapping corrected and access verified. Root cause: Azure AD authentication failure.</t>
-  </si>
-  <si>
     <t>Azure AD authentication failure</t>
   </si>
   <si>
@@ -1521,13 +1473,90 @@
   </si>
   <si>
     <t>Note: This is sample data, safe to edit and extend.</t>
+  </si>
+  <si>
+    <t>INC202602080071</t>
+  </si>
+  <si>
+    <t>Application: 500 Internal Server Error</t>
+  </si>
+  <si>
+    <t>Website is not woring and showing 500 Internal Server Error</t>
+  </si>
+  <si>
+    <t>3 -Low</t>
+  </si>
+  <si>
+    <t>The issue occurred because the database connection string was incorrect after deployment.</t>
+  </si>
+  <si>
+    <t>The database connection string was corrected in the configuration file. After restarting the application, the issue was resolved and tested successfully.
+Resolution Steps
+Reproduced the error from the application.
+Checked application logs and found a database connection failure.
+Verified the connection string in the configuration file.
+Found that the database server name was incorrect.
+Updated the correct database connection string.
+Restarted the application/service.
+Tested the application again.
+Confirmed that the API is working without 500 Internal Server Error.</t>
+  </si>
+  <si>
+    <t>1. Reproduced the login issue on the Customer Portal.</t>
+  </si>
+  <si>
+    <t>2. Verified user credentials and access permissions.</t>
+  </si>
+  <si>
+    <t>3. Checked application logs and authentication service logs.</t>
+  </si>
+  <si>
+    <t>4. Identified incorrect role/access mapping for affected users.</t>
+  </si>
+  <si>
+    <t>5. Updated the required user roles and access permissions.</t>
+  </si>
+  <si>
+    <t>6. Cleared browser cache/session and asked users to retry login.</t>
+  </si>
+  <si>
+    <t>7. Restarted the application service where required.</t>
+  </si>
+  <si>
+    <t>8. Validated login with affected user accounts.</t>
+  </si>
+  <si>
+    <t>9. Confirmed that users are now able to access the Customer Portal successfully.</t>
+  </si>
+  <si>
+    <t>Final Resolution</t>
+  </si>
+  <si>
+    <t>The access configuration was corrected, and required user permissions were updated. The Customer Portal login issue has been resolved and validated successfully.</t>
+  </si>
+  <si>
+    <t>Resolution Steps
+Reproduced the login issue on the Customer Portal.
+Verified user credentials and access permissions.
+Checked application logs and authentication service logs.
+Identified incorrect role/access mapping for affected users.
+Updated the required user roles and access permissions.
+Cleared browser cache/session and asked users to retry login.
+Restarted the application service where required.
+Validated login with affected user accounts.
+Confirmed that users are now able to access the Customer Portal successfully.
+Final Resolution
+The access configuration was corrected, and required user permissions were updated. The Customer Portal login issue has been resolved and validated successfully.</t>
+  </si>
+  <si>
+    <t>The issue occurred due to an authentication/access configuration problem in the Customer Portal, which prevented users from logging in successfully.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1551,6 +1580,14 @@
       <sz val="14"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <sz val="13.5"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1565,7 +1602,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1588,11 +1625,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF9E9E9E"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF9E9E9E"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1602,6 +1650,21 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1903,9 +1966,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB41"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:AB42"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -1928,7 +1991,7 @@
     <col min="28" max="28" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:28" ht="30" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2014,7 +2077,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:28" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:28" ht="42" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>28</v>
       </c>
@@ -2092,7 +2155,7 @@
       </c>
       <c r="AB2" s="2"/>
     </row>
-    <row r="3" spans="1:28" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:28" ht="42" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>50</v>
       </c>
@@ -2127,7 +2190,7 @@
         <v>37</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>59</v>
+        <v>192</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>60</v>
@@ -2157,11 +2220,11 @@
       <c r="V3" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="W3" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="X3" s="2" t="s">
-        <v>68</v>
+      <c r="W3" s="9" t="s">
+        <v>495</v>
+      </c>
+      <c r="X3" t="s">
+        <v>496</v>
       </c>
       <c r="Y3" s="2"/>
       <c r="Z3" s="2"/>
@@ -2170,30 +2233,30 @@
       </c>
       <c r="AB3" s="2"/>
     </row>
-    <row r="4" spans="1:28" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:28" ht="42" customHeight="1">
       <c r="A4" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>75</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>76</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>36</v>
@@ -2202,44 +2265,42 @@
         <v>36</v>
       </c>
       <c r="K4" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="L4" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="M4" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="M4" s="2" t="s">
+      <c r="N4" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="N4" s="2" t="s">
+      <c r="O4" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="O4" s="2" t="s">
+      <c r="P4" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="P4" s="2" t="s">
+      <c r="Q4" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="Q4" s="2" t="s">
+      <c r="R4" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="R4" s="2" t="s">
+      <c r="S4" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="S4" s="2" t="s">
+      <c r="T4" s="2" t="s">
         <v>85</v>
-      </c>
-      <c r="T4" s="2" t="s">
-        <v>86</v>
       </c>
       <c r="U4" s="2"/>
       <c r="V4" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="W4" s="2" t="s">
+      <c r="W4" s="8"/>
+      <c r="X4" s="2" t="s">
         <v>87</v>
-      </c>
-      <c r="X4" s="2" t="s">
-        <v>88</v>
       </c>
       <c r="Y4" s="2"/>
       <c r="Z4" s="2"/>
@@ -2248,30 +2309,30 @@
       </c>
       <c r="AB4" s="2"/>
     </row>
-    <row r="5" spans="1:28" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:28" ht="42" customHeight="1">
       <c r="A5" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>91</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>92</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>33</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>57</v>
@@ -2280,16 +2341,16 @@
         <v>58</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L5" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="N5" s="2" t="s">
         <v>94</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>95</v>
       </c>
       <c r="O5" s="2" t="s">
         <v>41</v>
@@ -2298,34 +2359,34 @@
         <v>62</v>
       </c>
       <c r="Q5" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="R5" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="R5" s="2" t="s">
+      <c r="S5" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="S5" s="2" t="s">
+      <c r="T5" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="T5" s="2" t="s">
+      <c r="U5" s="2" t="s">
         <v>99</v>
-      </c>
-      <c r="U5" s="2" t="s">
-        <v>100</v>
       </c>
       <c r="V5" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="W5" s="2" t="s">
+      <c r="W5" s="8" t="s">
+        <v>484</v>
+      </c>
+      <c r="X5" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="Y5" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="X5" s="2" t="s">
+      <c r="Z5" s="2" t="s">
         <v>102</v>
-      </c>
-      <c r="Y5" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="Z5" s="2" t="s">
-        <v>104</v>
       </c>
       <c r="AA5" s="2">
         <v>1</v>
@@ -2334,18 +2395,18 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:28" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:28" ht="42" customHeight="1">
       <c r="A6" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>106</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>108</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>53</v>
@@ -2354,10 +2415,10 @@
         <v>54</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>57</v>
@@ -2366,16 +2427,16 @@
         <v>36</v>
       </c>
       <c r="K6" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="L6" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="L6" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="M6" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O6" s="2" t="s">
         <v>41</v>
@@ -2384,26 +2445,26 @@
         <v>42</v>
       </c>
       <c r="Q6" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="R6" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="S6" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="R6" s="2" t="s">
+      <c r="T6" s="2" t="s">
         <v>113</v>
-      </c>
-      <c r="S6" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="T6" s="2" t="s">
-        <v>115</v>
       </c>
       <c r="U6" s="2"/>
       <c r="V6" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="W6" s="2" t="s">
-        <v>116</v>
+      <c r="W6" s="8" t="s">
+        <v>485</v>
       </c>
       <c r="X6" s="2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="Y6" s="2"/>
       <c r="Z6" s="2"/>
@@ -2414,30 +2475,30 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:28" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:28" ht="42" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>53</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>55</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>57</v>
@@ -2446,52 +2507,52 @@
         <v>58</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="N7" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="R7" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="S7" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="O7" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="P7" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q7" s="2" t="s">
+      <c r="T7" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="R7" s="2" t="s">
+      <c r="U7" s="2" t="s">
         <v>124</v>
-      </c>
-      <c r="S7" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="T7" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U7" s="2" t="s">
-        <v>127</v>
       </c>
       <c r="V7" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="W7" s="2" t="s">
-        <v>128</v>
+      <c r="W7" s="8" t="s">
+        <v>486</v>
       </c>
       <c r="X7" s="2" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="Y7" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="Z7" s="2" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="AA7" s="2">
         <v>0</v>
@@ -2500,30 +2561,30 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:28" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:28" ht="42" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>33</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>57</v>
@@ -2532,44 +2593,44 @@
         <v>58</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>38</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="O8" s="2" t="s">
         <v>41</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="U8" s="2"/>
       <c r="V8" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="W8" s="2" t="s">
-        <v>141</v>
+      <c r="W8" s="8" t="s">
+        <v>487</v>
       </c>
       <c r="X8" s="2" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="Y8" s="2"/>
       <c r="Z8" s="2"/>
@@ -2578,27 +2639,27 @@
       </c>
       <c r="AB8" s="2"/>
     </row>
-    <row r="9" spans="1:28" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:28" ht="42" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="F9" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="G9" s="2" t="s">
         <v>74</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>75</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>56</v>
@@ -2613,41 +2674,41 @@
         <v>37</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="P9" s="2" t="s">
         <v>42</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="U9" s="2"/>
       <c r="V9" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="W9" s="2" t="s">
-        <v>153</v>
+      <c r="W9" s="8" t="s">
+        <v>488</v>
       </c>
       <c r="X9" s="2" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="Y9" s="2"/>
       <c r="Z9" s="2"/>
@@ -2658,21 +2719,21 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:28" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:28" ht="42" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>54</v>
@@ -2696,38 +2757,38 @@
         <v>59</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="N10" s="2" t="s">
         <v>40</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="P10" s="2" t="s">
         <v>62</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="S10" s="2" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="U10" s="2"/>
       <c r="V10" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="W10" s="2" t="s">
-        <v>163</v>
+      <c r="W10" s="8" t="s">
+        <v>489</v>
       </c>
       <c r="X10" s="2" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="Y10" s="2"/>
       <c r="Z10" s="2"/>
@@ -2736,27 +2797,27 @@
       </c>
       <c r="AB10" s="2"/>
     </row>
-    <row r="11" spans="1:28" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:28" ht="42" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>35</v>
@@ -2768,44 +2829,44 @@
         <v>57</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>59</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="O11" s="2" t="s">
         <v>41</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="U11" s="2"/>
       <c r="V11" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="W11" s="2" t="s">
-        <v>173</v>
+      <c r="W11" s="8" t="s">
+        <v>490</v>
       </c>
       <c r="X11" s="2" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="Y11" s="2"/>
       <c r="Z11" s="2"/>
@@ -2816,30 +2877,30 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:28" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:28" ht="42" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>32</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>58</v>
@@ -2848,44 +2909,44 @@
         <v>57</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>59</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="T12" s="2" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="U12" s="2"/>
       <c r="V12" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="W12" s="2" t="s">
-        <v>186</v>
+      <c r="W12" s="8" t="s">
+        <v>491</v>
       </c>
       <c r="X12" s="2" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="Y12" s="2"/>
       <c r="Z12" s="2"/>
@@ -2896,30 +2957,30 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:28" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:28" ht="42" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>33</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>36</v>
@@ -2928,44 +2989,44 @@
         <v>57</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>38</v>
+        <v>192</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="P13" s="2" t="s">
         <v>42</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="T13" s="2" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="U13" s="2"/>
       <c r="V13" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="W13" s="2" t="s">
-        <v>196</v>
+      <c r="W13" s="8" t="s">
+        <v>492</v>
       </c>
       <c r="X13" s="2" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="Y13" s="2"/>
       <c r="Z13" s="2"/>
@@ -2974,30 +3035,30 @@
       </c>
       <c r="AB13" s="2"/>
     </row>
-    <row r="14" spans="1:28" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:28" ht="42" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="E14" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G14" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="F14" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>93</v>
-      </c>
       <c r="H14" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>36</v>
@@ -3006,82 +3067,79 @@
         <v>36</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="M14" s="2" t="s">
         <v>60</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="R14" s="2" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="T14" s="2" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="U14" s="2" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="V14" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="W14" s="2" t="s">
-        <v>209</v>
-      </c>
       <c r="X14" s="2" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="Y14" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="Z14" s="2" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="AA14" s="2">
         <v>0</v>
       </c>
       <c r="AB14" s="2"/>
     </row>
-    <row r="15" spans="1:28" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:28" ht="42" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G15" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H15" s="2" t="s">
         <v>75</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>76</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>57</v>
@@ -3090,52 +3148,52 @@
         <v>57</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="M15" s="2" t="s">
         <v>39</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="T15" s="2" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="U15" s="2" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="V15" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="W15" s="2" t="s">
-        <v>218</v>
+      <c r="W15" s="7" t="s">
+        <v>493</v>
       </c>
       <c r="X15" s="2" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="Y15" s="2" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="Z15" s="2" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="AA15" s="2">
         <v>0</v>
@@ -3144,27 +3202,27 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:28" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:28" ht="42" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="E16" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F16" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="F16" s="2" t="s">
-        <v>74</v>
-      </c>
       <c r="G16" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>56</v>
@@ -3176,44 +3234,41 @@
         <v>57</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="P16" s="2" t="s">
         <v>42</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="R16" s="2" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="S16" s="2" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="T16" s="2" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="U16" s="2"/>
       <c r="V16" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="W16" s="2" t="s">
-        <v>230</v>
-      </c>
       <c r="X16" s="2" t="s">
-        <v>231</v>
+        <v>218</v>
       </c>
       <c r="Y16" s="2"/>
       <c r="Z16" s="2"/>
@@ -3224,27 +3279,27 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:28" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:28" ht="42" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>232</v>
+        <v>219</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>233</v>
+        <v>220</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>234</v>
+        <v>221</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>33</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>56</v>
@@ -3259,49 +3314,49 @@
         <v>37</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>94</v>
+        <v>192</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="N17" s="2" t="s">
         <v>61</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>235</v>
+        <v>222</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>236</v>
+        <v>223</v>
       </c>
       <c r="R17" s="2" t="s">
-        <v>237</v>
+        <v>224</v>
       </c>
       <c r="S17" s="2" t="s">
-        <v>238</v>
+        <v>225</v>
       </c>
       <c r="T17" s="2" t="s">
-        <v>239</v>
+        <v>226</v>
       </c>
       <c r="U17" s="2" t="s">
-        <v>240</v>
+        <v>227</v>
       </c>
       <c r="V17" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="W17" s="2" t="s">
-        <v>241</v>
+      <c r="W17" t="s">
+        <v>494</v>
       </c>
       <c r="X17" s="2" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="Y17" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="Z17" s="2" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
       <c r="AA17" s="2">
         <v>0</v>
@@ -3310,30 +3365,30 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:28" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:28" ht="42" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>244</v>
+        <v>230</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>58</v>
@@ -3342,76 +3397,76 @@
         <v>36</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="M18" s="2" t="s">
         <v>39</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O18" s="2" t="s">
         <v>41</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="R18" s="2" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
       <c r="S18" s="2" t="s">
-        <v>250</v>
+        <v>236</v>
       </c>
       <c r="T18" s="2" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="U18" s="2" t="s">
-        <v>250</v>
+        <v>236</v>
       </c>
       <c r="V18" s="2" t="s">
         <v>47</v>
       </c>
       <c r="W18" s="2" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="X18" s="2" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="Y18" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="Z18" s="2" t="s">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="AA18" s="2">
         <v>0</v>
       </c>
       <c r="AB18" s="2"/>
     </row>
-    <row r="19" spans="1:28" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:28" ht="42" customHeight="1">
       <c r="A19" s="2" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>256</v>
+        <v>242</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>257</v>
+        <v>243</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>55</v>
@@ -3426,10 +3481,10 @@
         <v>58</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="M19" s="2" t="s">
         <v>60</v>
@@ -3438,32 +3493,32 @@
         <v>61</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="P19" s="2" t="s">
         <v>62</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>258</v>
+        <v>244</v>
       </c>
       <c r="R19" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S19" s="2" t="s">
-        <v>259</v>
+        <v>245</v>
       </c>
       <c r="T19" s="2" t="s">
-        <v>260</v>
+        <v>246</v>
       </c>
       <c r="U19" s="2"/>
       <c r="V19" s="2" t="s">
         <v>47</v>
       </c>
       <c r="W19" s="2" t="s">
-        <v>261</v>
+        <v>247</v>
       </c>
       <c r="X19" s="2" t="s">
-        <v>262</v>
+        <v>248</v>
       </c>
       <c r="Y19" s="2"/>
       <c r="Z19" s="2"/>
@@ -3474,30 +3529,30 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:28" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:28" ht="42" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>263</v>
+        <v>249</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>264</v>
+        <v>250</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>36</v>
@@ -3506,44 +3561,44 @@
         <v>57</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>266</v>
+        <v>252</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="P20" s="2" t="s">
         <v>42</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>267</v>
+        <v>253</v>
       </c>
       <c r="R20" s="2" t="s">
-        <v>268</v>
+        <v>254</v>
       </c>
       <c r="S20" s="2" t="s">
-        <v>269</v>
+        <v>255</v>
       </c>
       <c r="T20" s="2" t="s">
-        <v>270</v>
+        <v>256</v>
       </c>
       <c r="U20" s="2"/>
       <c r="V20" s="2" t="s">
         <v>47</v>
       </c>
       <c r="W20" s="2" t="s">
-        <v>271</v>
+        <v>257</v>
       </c>
       <c r="X20" s="2" t="s">
-        <v>272</v>
+        <v>258</v>
       </c>
       <c r="Y20" s="2"/>
       <c r="Z20" s="2"/>
@@ -3554,24 +3609,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:28" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:28" ht="42" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>273</v>
+        <v>259</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>274</v>
+        <v>260</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>275</v>
+        <v>261</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>276</v>
+        <v>262</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>55</v>
@@ -3589,41 +3644,41 @@
         <v>37</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>266</v>
+        <v>252</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="N21" s="2" t="s">
         <v>40</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>235</v>
+        <v>222</v>
       </c>
       <c r="Q21" s="2" t="s">
-        <v>277</v>
+        <v>263</v>
       </c>
       <c r="R21" s="2" t="s">
-        <v>278</v>
+        <v>264</v>
       </c>
       <c r="S21" s="2" t="s">
-        <v>279</v>
+        <v>265</v>
       </c>
       <c r="T21" s="2" t="s">
-        <v>280</v>
+        <v>266</v>
       </c>
       <c r="U21" s="2"/>
       <c r="V21" s="2" t="s">
         <v>47</v>
       </c>
       <c r="W21" s="2" t="s">
-        <v>281</v>
+        <v>267</v>
       </c>
       <c r="X21" s="2" t="s">
-        <v>282</v>
+        <v>268</v>
       </c>
       <c r="Y21" s="2"/>
       <c r="Z21" s="2"/>
@@ -3634,30 +3689,30 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:28" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:28" ht="42" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>283</v>
+        <v>269</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>284</v>
+        <v>270</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>285</v>
+        <v>271</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>57</v>
@@ -3666,16 +3721,16 @@
         <v>58</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O22" s="2" t="s">
         <v>41</v>
@@ -3684,23 +3739,23 @@
         <v>42</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>286</v>
+        <v>272</v>
       </c>
       <c r="R22" s="2" t="s">
-        <v>287</v>
+        <v>273</v>
       </c>
       <c r="S22" s="2" t="s">
-        <v>288</v>
+        <v>274</v>
       </c>
       <c r="T22" s="2" t="s">
-        <v>289</v>
+        <v>275</v>
       </c>
       <c r="U22" s="2"/>
       <c r="V22" s="2" t="s">
         <v>47</v>
       </c>
       <c r="W22" s="2" t="s">
-        <v>290</v>
+        <v>276</v>
       </c>
       <c r="X22" s="2" t="s">
         <v>49</v>
@@ -3712,18 +3767,18 @@
       </c>
       <c r="AB22" s="2"/>
     </row>
-    <row r="23" spans="1:28" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:28" ht="42" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>292</v>
+        <v>278</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>293</v>
+        <v>279</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>32</v>
@@ -3732,10 +3787,10 @@
         <v>33</v>
       </c>
       <c r="G23" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H23" s="2" t="s">
         <v>75</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>76</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>57</v>
@@ -3744,44 +3799,44 @@
         <v>36</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>266</v>
+        <v>252</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="Q23" s="2" t="s">
-        <v>294</v>
+        <v>280</v>
       </c>
       <c r="R23" s="2" t="s">
-        <v>295</v>
+        <v>281</v>
       </c>
       <c r="S23" s="2" t="s">
-        <v>296</v>
+        <v>282</v>
       </c>
       <c r="T23" s="2" t="s">
-        <v>297</v>
+        <v>283</v>
       </c>
       <c r="U23" s="2"/>
       <c r="V23" s="2" t="s">
         <v>47</v>
       </c>
       <c r="W23" s="2" t="s">
-        <v>298</v>
+        <v>284</v>
       </c>
       <c r="X23" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="Y23" s="2"/>
       <c r="Z23" s="2"/>
@@ -3790,30 +3845,30 @@
       </c>
       <c r="AB23" s="2"/>
     </row>
-    <row r="24" spans="1:28" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:28" ht="42" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>299</v>
+        <v>285</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>300</v>
+        <v>286</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>301</v>
+        <v>287</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>53</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>55</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>36</v>
@@ -3825,13 +3880,13 @@
         <v>37</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>38</v>
+        <v>192</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="O24" s="2" t="s">
         <v>41</v>
@@ -3840,26 +3895,26 @@
         <v>42</v>
       </c>
       <c r="Q24" s="2" t="s">
-        <v>302</v>
+        <v>288</v>
       </c>
       <c r="R24" s="2" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="S24" s="2" t="s">
-        <v>303</v>
+        <v>289</v>
       </c>
       <c r="T24" s="2" t="s">
-        <v>304</v>
+        <v>290</v>
       </c>
       <c r="U24" s="2"/>
       <c r="V24" s="2" t="s">
         <v>47</v>
       </c>
       <c r="W24" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="X24" s="2" t="s">
         <v>87</v>
-      </c>
-      <c r="X24" s="2" t="s">
-        <v>88</v>
       </c>
       <c r="Y24" s="2"/>
       <c r="Z24" s="2"/>
@@ -3870,30 +3925,30 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:28" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:28" ht="42" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>305</v>
+        <v>291</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>306</v>
+        <v>292</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>307</v>
+        <v>293</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>33</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>58</v>
@@ -3902,16 +3957,16 @@
         <v>58</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="L25" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="M25" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="M25" s="2" t="s">
-        <v>79</v>
-      </c>
       <c r="N25" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O25" s="2" t="s">
         <v>41</v>
@@ -3920,26 +3975,26 @@
         <v>42</v>
       </c>
       <c r="Q25" s="2" t="s">
-        <v>308</v>
+        <v>294</v>
       </c>
       <c r="R25" s="2" t="s">
-        <v>309</v>
+        <v>295</v>
       </c>
       <c r="S25" s="2" t="s">
-        <v>310</v>
+        <v>296</v>
       </c>
       <c r="T25" s="2" t="s">
-        <v>311</v>
+        <v>297</v>
       </c>
       <c r="U25" s="2"/>
       <c r="V25" s="2" t="s">
         <v>47</v>
       </c>
       <c r="W25" s="2" t="s">
-        <v>312</v>
+        <v>298</v>
       </c>
       <c r="X25" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="Y25" s="2"/>
       <c r="Z25" s="2"/>
@@ -3948,30 +4003,30 @@
       </c>
       <c r="AB25" s="2"/>
     </row>
-    <row r="26" spans="1:28" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:28" ht="42" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>313</v>
+        <v>299</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>314</v>
+        <v>300</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>315</v>
+        <v>301</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>32</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>36</v>
@@ -3980,13 +4035,13 @@
         <v>58</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="N26" s="2" t="s">
         <v>40</v>
@@ -3995,29 +4050,29 @@
         <v>41</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="Q26" s="2" t="s">
-        <v>316</v>
+        <v>302</v>
       </c>
       <c r="R26" s="2" t="s">
-        <v>317</v>
+        <v>303</v>
       </c>
       <c r="S26" s="2" t="s">
-        <v>318</v>
+        <v>304</v>
       </c>
       <c r="T26" s="2" t="s">
-        <v>319</v>
+        <v>305</v>
       </c>
       <c r="U26" s="2"/>
       <c r="V26" s="2" t="s">
         <v>47</v>
       </c>
       <c r="W26" s="2" t="s">
-        <v>320</v>
+        <v>306</v>
       </c>
       <c r="X26" s="2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="Y26" s="2"/>
       <c r="Z26" s="2"/>
@@ -4028,27 +4083,27 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:28" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:28" ht="42" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>321</v>
+        <v>307</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>35</v>
@@ -4063,41 +4118,41 @@
         <v>37</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M27" s="2" t="s">
         <v>60</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O27" s="2" t="s">
         <v>41</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="Q27" s="2" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="R27" s="2" t="s">
-        <v>323</v>
+        <v>309</v>
       </c>
       <c r="S27" s="2" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="T27" s="2" t="s">
-        <v>324</v>
+        <v>310</v>
       </c>
       <c r="U27" s="2"/>
       <c r="V27" s="2" t="s">
         <v>47</v>
       </c>
       <c r="W27" s="2" t="s">
-        <v>325</v>
+        <v>311</v>
       </c>
       <c r="X27" s="2" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="Y27" s="2"/>
       <c r="Z27" s="2"/>
@@ -4108,30 +4163,30 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:28" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:28" ht="42" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>327</v>
+        <v>313</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>328</v>
+        <v>314</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>54</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>58</v>
@@ -4140,82 +4195,82 @@
         <v>57</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>94</v>
+        <v>192</v>
       </c>
       <c r="M28" s="2" t="s">
         <v>39</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O28" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="P28" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="P28" s="2" t="s">
-        <v>82</v>
-      </c>
       <c r="Q28" s="2" t="s">
-        <v>329</v>
+        <v>315</v>
       </c>
       <c r="R28" s="2" t="s">
-        <v>330</v>
+        <v>316</v>
       </c>
       <c r="S28" s="2" t="s">
-        <v>331</v>
+        <v>317</v>
       </c>
       <c r="T28" s="2" t="s">
-        <v>332</v>
+        <v>318</v>
       </c>
       <c r="U28" s="2" t="s">
-        <v>333</v>
+        <v>319</v>
       </c>
       <c r="V28" s="2" t="s">
         <v>47</v>
       </c>
       <c r="W28" s="2" t="s">
-        <v>334</v>
+        <v>320</v>
       </c>
       <c r="X28" s="2" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="Y28" s="2" t="s">
-        <v>335</v>
+        <v>321</v>
       </c>
       <c r="Z28" s="2" t="s">
-        <v>336</v>
+        <v>322</v>
       </c>
       <c r="AA28" s="2">
         <v>2</v>
       </c>
       <c r="AB28" s="2"/>
     </row>
-    <row r="29" spans="1:28" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:28" ht="42" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>337</v>
+        <v>323</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>338</v>
+        <v>324</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>339</v>
+        <v>325</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>53</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>36</v>
@@ -4224,44 +4279,44 @@
         <v>58</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>266</v>
+        <v>252</v>
       </c>
       <c r="M29" s="2" t="s">
         <v>60</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>235</v>
+        <v>222</v>
       </c>
       <c r="Q29" s="2" t="s">
-        <v>296</v>
+        <v>282</v>
       </c>
       <c r="R29" s="2" t="s">
-        <v>340</v>
+        <v>326</v>
       </c>
       <c r="S29" s="2" t="s">
-        <v>340</v>
+        <v>326</v>
       </c>
       <c r="T29" s="2" t="s">
-        <v>329</v>
+        <v>315</v>
       </c>
       <c r="U29" s="2"/>
       <c r="V29" s="2" t="s">
         <v>47</v>
       </c>
       <c r="W29" s="2" t="s">
-        <v>341</v>
+        <v>327</v>
       </c>
       <c r="X29" s="2" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="Y29" s="2"/>
       <c r="Z29" s="2"/>
@@ -4272,27 +4327,27 @@
         <v>3</v>
       </c>
     </row>
-    <row r="30" spans="1:28" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:28" ht="42" customHeight="1">
       <c r="A30" s="2" t="s">
-        <v>342</v>
+        <v>328</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>233</v>
+        <v>220</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>343</v>
+        <v>329</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>33</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>35</v>
@@ -4304,52 +4359,52 @@
         <v>58</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="N30" s="2" t="s">
         <v>61</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="P30" s="2" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="Q30" s="2" t="s">
-        <v>344</v>
+        <v>330</v>
       </c>
       <c r="R30" s="2" t="s">
-        <v>345</v>
+        <v>331</v>
       </c>
       <c r="S30" s="2" t="s">
-        <v>346</v>
+        <v>332</v>
       </c>
       <c r="T30" s="2" t="s">
-        <v>347</v>
+        <v>333</v>
       </c>
       <c r="U30" s="2" t="s">
-        <v>348</v>
+        <v>334</v>
       </c>
       <c r="V30" s="2" t="s">
         <v>47</v>
       </c>
       <c r="W30" s="2" t="s">
-        <v>349</v>
+        <v>335</v>
       </c>
       <c r="X30" s="2" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="Y30" s="2" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="Z30" s="2" t="s">
-        <v>350</v>
+        <v>336</v>
       </c>
       <c r="AA30" s="2">
         <v>0</v>
@@ -4358,27 +4413,27 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:28" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:28" ht="42" customHeight="1">
       <c r="A31" s="2" t="s">
-        <v>351</v>
+        <v>337</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>352</v>
+        <v>338</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>353</v>
+        <v>339</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>56</v>
@@ -4390,44 +4445,44 @@
         <v>58</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>59</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="P31" s="2" t="s">
-        <v>235</v>
+        <v>222</v>
       </c>
       <c r="Q31" s="2" t="s">
-        <v>354</v>
+        <v>340</v>
       </c>
       <c r="R31" s="2" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="S31" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T31" s="2" t="s">
-        <v>355</v>
+        <v>341</v>
       </c>
       <c r="U31" s="2"/>
       <c r="V31" s="2" t="s">
         <v>47</v>
       </c>
       <c r="W31" s="2" t="s">
-        <v>356</v>
+        <v>342</v>
       </c>
       <c r="X31" s="2" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="Y31" s="2"/>
       <c r="Z31" s="2"/>
@@ -4436,30 +4491,30 @@
       </c>
       <c r="AB31" s="2"/>
     </row>
-    <row r="32" spans="1:28" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:28" ht="42" customHeight="1">
       <c r="A32" s="2" t="s">
-        <v>357</v>
+        <v>343</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>358</v>
+        <v>344</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>32</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G32" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H32" s="2" t="s">
         <v>75</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>76</v>
       </c>
       <c r="I32" s="2" t="s">
         <v>58</v>
@@ -4471,7 +4526,7 @@
         <v>37</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M32" s="2" t="s">
         <v>60</v>
@@ -4480,32 +4535,32 @@
         <v>61</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="P32" s="2" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="Q32" s="2" t="s">
-        <v>359</v>
+        <v>345</v>
       </c>
       <c r="R32" s="2" t="s">
-        <v>360</v>
+        <v>346</v>
       </c>
       <c r="S32" s="2" t="s">
-        <v>361</v>
+        <v>347</v>
       </c>
       <c r="T32" s="2" t="s">
-        <v>362</v>
+        <v>348</v>
       </c>
       <c r="U32" s="2"/>
       <c r="V32" s="2" t="s">
         <v>47</v>
       </c>
       <c r="W32" s="2" t="s">
-        <v>363</v>
+        <v>349</v>
       </c>
       <c r="X32" s="2" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="Y32" s="2"/>
       <c r="Z32" s="2"/>
@@ -4516,30 +4571,30 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="1:28" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:28" ht="42" customHeight="1">
       <c r="A33" s="2" t="s">
-        <v>364</v>
+        <v>350</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>365</v>
+        <v>351</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>366</v>
+        <v>352</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="G33" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H33" s="2" t="s">
         <v>75</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>76</v>
       </c>
       <c r="I33" s="2" t="s">
         <v>36</v>
@@ -4551,25 +4606,25 @@
         <v>37</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>266</v>
+        <v>252</v>
       </c>
       <c r="M33" s="2" t="s">
         <v>60</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="P33" s="2" t="s">
-        <v>235</v>
+        <v>222</v>
       </c>
       <c r="Q33" s="2" t="s">
         <v>63</v>
       </c>
       <c r="R33" s="2" t="s">
-        <v>367</v>
+        <v>353</v>
       </c>
       <c r="S33" s="2" t="s">
         <v>65</v>
@@ -4582,10 +4637,10 @@
         <v>47</v>
       </c>
       <c r="W33" s="2" t="s">
-        <v>368</v>
+        <v>354</v>
       </c>
       <c r="X33" s="2" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="Y33" s="2"/>
       <c r="Z33" s="2"/>
@@ -4594,21 +4649,21 @@
       </c>
       <c r="AB33" s="2"/>
     </row>
-    <row r="34" spans="1:28" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:28" ht="42" customHeight="1">
       <c r="A34" s="2" t="s">
-        <v>369</v>
+        <v>355</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>370</v>
+        <v>356</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>371</v>
+        <v>357</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>54</v>
@@ -4617,7 +4672,7 @@
         <v>55</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>57</v>
@@ -4626,16 +4681,16 @@
         <v>57</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>266</v>
+        <v>252</v>
       </c>
       <c r="M34" s="2" t="s">
         <v>60</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O34" s="2" t="s">
         <v>41</v>
@@ -4644,26 +4699,26 @@
         <v>42</v>
       </c>
       <c r="Q34" s="2" t="s">
-        <v>372</v>
+        <v>358</v>
       </c>
       <c r="R34" s="2" t="s">
-        <v>373</v>
+        <v>359</v>
       </c>
       <c r="S34" s="2" t="s">
-        <v>374</v>
+        <v>360</v>
       </c>
       <c r="T34" s="2" t="s">
-        <v>375</v>
+        <v>361</v>
       </c>
       <c r="U34" s="2"/>
       <c r="V34" s="2" t="s">
         <v>47</v>
       </c>
       <c r="W34" s="2" t="s">
-        <v>376</v>
+        <v>362</v>
       </c>
       <c r="X34" s="2" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="Y34" s="2"/>
       <c r="Z34" s="2"/>
@@ -4674,27 +4729,27 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:28" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:28" ht="42" customHeight="1">
       <c r="A35" s="2" t="s">
-        <v>377</v>
+        <v>363</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>378</v>
+        <v>364</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>379</v>
+        <v>365</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>35</v>
@@ -4706,44 +4761,44 @@
         <v>58</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="L35" s="2" t="s">
         <v>59</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>380</v>
+        <v>366</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P35" s="2" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="Q35" s="2" t="s">
-        <v>381</v>
+        <v>367</v>
       </c>
       <c r="R35" s="2" t="s">
-        <v>382</v>
+        <v>368</v>
       </c>
       <c r="S35" s="2" t="s">
-        <v>383</v>
+        <v>369</v>
       </c>
       <c r="T35" s="2" t="s">
-        <v>329</v>
+        <v>315</v>
       </c>
       <c r="U35" s="2"/>
       <c r="V35" s="2" t="s">
         <v>47</v>
       </c>
       <c r="W35" s="2" t="s">
-        <v>384</v>
+        <v>370</v>
       </c>
       <c r="X35" s="2" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="Y35" s="2"/>
       <c r="Z35" s="2"/>
@@ -4754,24 +4809,24 @@
         <v>5</v>
       </c>
     </row>
-    <row r="36" spans="1:28" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:28" ht="42" customHeight="1">
       <c r="A36" s="2" t="s">
-        <v>385</v>
+        <v>371</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>386</v>
+        <v>372</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>387</v>
+        <v>373</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>32</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>276</v>
+        <v>262</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>34</v>
@@ -4789,41 +4844,41 @@
         <v>37</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>266</v>
+        <v>252</v>
       </c>
       <c r="M36" s="2" t="s">
         <v>39</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P36" s="2" t="s">
         <v>42</v>
       </c>
       <c r="Q36" s="2" t="s">
-        <v>388</v>
+        <v>374</v>
       </c>
       <c r="R36" s="2" t="s">
-        <v>389</v>
+        <v>375</v>
       </c>
       <c r="S36" s="2" t="s">
-        <v>390</v>
+        <v>376</v>
       </c>
       <c r="T36" s="2" t="s">
-        <v>391</v>
+        <v>377</v>
       </c>
       <c r="U36" s="2"/>
       <c r="V36" s="2" t="s">
         <v>47</v>
       </c>
       <c r="W36" s="2" t="s">
-        <v>392</v>
+        <v>378</v>
       </c>
       <c r="X36" s="2" t="s">
-        <v>231</v>
+        <v>218</v>
       </c>
       <c r="Y36" s="2"/>
       <c r="Z36" s="2"/>
@@ -4834,27 +4889,27 @@
         <v>4</v>
       </c>
     </row>
-    <row r="37" spans="1:28" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:28" ht="42" customHeight="1">
       <c r="A37" s="2" t="s">
-        <v>393</v>
+        <v>379</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>394</v>
+        <v>380</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>395</v>
+        <v>381</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>54</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>35</v>
@@ -4866,44 +4921,44 @@
         <v>36</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="P37" s="2" t="s">
         <v>42</v>
       </c>
       <c r="Q37" s="2" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="R37" s="2" t="s">
-        <v>396</v>
+        <v>382</v>
       </c>
       <c r="S37" s="2" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="T37" s="2" t="s">
-        <v>277</v>
+        <v>263</v>
       </c>
       <c r="U37" s="2"/>
       <c r="V37" s="2" t="s">
         <v>47</v>
       </c>
       <c r="W37" s="2" t="s">
-        <v>397</v>
+        <v>383</v>
       </c>
       <c r="X37" s="2" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="Y37" s="2"/>
       <c r="Z37" s="2"/>
@@ -4914,24 +4969,24 @@
         <v>4</v>
       </c>
     </row>
-    <row r="38" spans="1:28" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:28" ht="42" customHeight="1">
       <c r="A38" s="2" t="s">
-        <v>398</v>
+        <v>384</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>399</v>
+        <v>385</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>400</v>
+        <v>386</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>55</v>
@@ -4946,44 +5001,44 @@
         <v>57</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="L38" s="2" t="s">
         <v>38</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="P38" s="2" t="s">
-        <v>235</v>
+        <v>222</v>
       </c>
       <c r="Q38" s="2" t="s">
-        <v>401</v>
+        <v>387</v>
       </c>
       <c r="R38" s="2" t="s">
-        <v>402</v>
+        <v>388</v>
       </c>
       <c r="S38" s="2" t="s">
-        <v>403</v>
+        <v>389</v>
       </c>
       <c r="T38" s="2" t="s">
-        <v>404</v>
+        <v>390</v>
       </c>
       <c r="U38" s="2"/>
       <c r="V38" s="2" t="s">
         <v>47</v>
       </c>
       <c r="W38" s="2" t="s">
-        <v>405</v>
+        <v>391</v>
       </c>
       <c r="X38" s="2" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="Y38" s="2"/>
       <c r="Z38" s="2"/>
@@ -4994,30 +5049,30 @@
         <v>4</v>
       </c>
     </row>
-    <row r="39" spans="1:28" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:28" ht="42" customHeight="1">
       <c r="A39" s="2" t="s">
-        <v>406</v>
+        <v>392</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>407</v>
+        <v>393</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>408</v>
+        <v>394</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>53</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I39" s="2" t="s">
         <v>36</v>
@@ -5026,44 +5081,44 @@
         <v>58</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M39" s="2" t="s">
         <v>39</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="P39" s="2" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="Q39" s="2" t="s">
-        <v>409</v>
+        <v>395</v>
       </c>
       <c r="R39" s="2" t="s">
-        <v>410</v>
+        <v>396</v>
       </c>
       <c r="S39" s="2" t="s">
-        <v>411</v>
+        <v>397</v>
       </c>
       <c r="T39" s="2" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="U39" s="2"/>
       <c r="V39" s="2" t="s">
         <v>47</v>
       </c>
       <c r="W39" s="2" t="s">
-        <v>412</v>
+        <v>398</v>
       </c>
       <c r="X39" s="2" t="s">
-        <v>262</v>
+        <v>248</v>
       </c>
       <c r="Y39" s="2"/>
       <c r="Z39" s="2"/>
@@ -5074,27 +5129,27 @@
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="1:28" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:28" ht="42" customHeight="1">
       <c r="A40" s="2" t="s">
-        <v>413</v>
+        <v>399</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>414</v>
+        <v>400</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>415</v>
+        <v>401</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>33</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>56</v>
@@ -5106,52 +5161,52 @@
         <v>58</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>94</v>
+        <v>192</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="N40" s="2" t="s">
         <v>40</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="P40" s="2" t="s">
         <v>42</v>
       </c>
       <c r="Q40" s="2" t="s">
-        <v>416</v>
+        <v>402</v>
       </c>
       <c r="R40" s="2" t="s">
-        <v>417</v>
+        <v>403</v>
       </c>
       <c r="S40" s="2" t="s">
-        <v>418</v>
+        <v>404</v>
       </c>
       <c r="T40" s="2" t="s">
-        <v>286</v>
+        <v>272</v>
       </c>
       <c r="U40" s="2" t="s">
-        <v>288</v>
+        <v>274</v>
       </c>
       <c r="V40" s="2" t="s">
         <v>47</v>
       </c>
       <c r="W40" s="2" t="s">
-        <v>419</v>
+        <v>405</v>
       </c>
       <c r="X40" s="2" t="s">
-        <v>272</v>
+        <v>258</v>
       </c>
       <c r="Y40" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="Z40" s="2" t="s">
-        <v>420</v>
+        <v>406</v>
       </c>
       <c r="AA40" s="2">
         <v>0</v>
@@ -5160,27 +5215,27 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="1:28" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:28" ht="42" customHeight="1">
       <c r="A41" s="2" t="s">
-        <v>421</v>
+        <v>407</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>422</v>
+        <v>408</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>423</v>
+        <v>409</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>56</v>
@@ -5192,44 +5247,44 @@
         <v>58</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>380</v>
+        <v>366</v>
       </c>
       <c r="O41" s="2" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="P41" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="Q41" s="2" t="s">
-        <v>424</v>
+        <v>410</v>
       </c>
       <c r="R41" s="2" t="s">
-        <v>425</v>
+        <v>411</v>
       </c>
       <c r="S41" s="2" t="s">
-        <v>426</v>
+        <v>412</v>
       </c>
       <c r="T41" s="2" t="s">
-        <v>427</v>
+        <v>413</v>
       </c>
       <c r="U41" s="2"/>
       <c r="V41" s="2" t="s">
         <v>47</v>
       </c>
       <c r="W41" s="2" t="s">
-        <v>428</v>
+        <v>414</v>
       </c>
       <c r="X41" s="2" t="s">
-        <v>282</v>
+        <v>268</v>
       </c>
       <c r="Y41" s="2"/>
       <c r="Z41" s="2"/>
@@ -5240,85 +5295,155 @@
         <v>5</v>
       </c>
     </row>
+    <row r="42" spans="1:28" ht="288">
+      <c r="A42" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>479</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>480</v>
+      </c>
+      <c r="E42" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="F42" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G42" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="H42" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="I42" s="5" t="s">
+        <v>481</v>
+      </c>
+      <c r="J42" s="5" t="s">
+        <v>481</v>
+      </c>
+      <c r="K42" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="L42" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="M42" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="N42" s="5" t="s">
+        <v>366</v>
+      </c>
+      <c r="O42" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="P42" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q42" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="R42" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="S42" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="T42" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="V42" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="W42" s="6" t="s">
+        <v>483</v>
+      </c>
+      <c r="X42" t="s">
+        <v>482</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AB41" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="13">
-        <x14:dataValidation type="list" allowBlank="1" showDropDown="1" xr:uid="{00000000-0002-0000-0000-000000000000}">
+        <x14:dataValidation type="list" allowBlank="1" showDropDown="1">
           <x14:formula1>
             <xm:f>Lists!$B$2:$B$5</xm:f>
           </x14:formula1>
           <xm:sqref>B2:B500</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showDropDown="1" xr:uid="{00000000-0002-0000-0000-000001000000}">
+        <x14:dataValidation type="list" allowBlank="1" showDropDown="1">
           <x14:formula1>
             <xm:f>Lists!$B$28:$B$33</xm:f>
           </x14:formula1>
           <xm:sqref>E2:E500</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showDropDown="1" xr:uid="{00000000-0002-0000-0000-000002000000}">
+        <x14:dataValidation type="list" allowBlank="1" showDropDown="1">
           <x14:formula1>
             <xm:f>Lists!$B$35:$B$41</xm:f>
           </x14:formula1>
           <xm:sqref>F2:F500</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showDropDown="1" xr:uid="{00000000-0002-0000-0000-000003000000}">
+        <x14:dataValidation type="list" allowBlank="1" showDropDown="1">
           <x14:formula1>
             <xm:f>Lists!$B$82:$B$88</xm:f>
           </x14:formula1>
           <xm:sqref>G2:G500</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showDropDown="1" xr:uid="{00000000-0002-0000-0000-000004000000}">
+        <x14:dataValidation type="list" allowBlank="1" showDropDown="1">
           <x14:formula1>
             <xm:f>Lists!$B$65:$B$68</xm:f>
           </x14:formula1>
           <xm:sqref>H2:H500</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showDropDown="1" xr:uid="{00000000-0002-0000-0000-000005000000}">
+        <x14:dataValidation type="list" allowBlank="1" showDropDown="1">
           <x14:formula1>
             <xm:f>Lists!$B$20:$B$22</xm:f>
           </x14:formula1>
           <xm:sqref>I2:I500</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showDropDown="1" xr:uid="{00000000-0002-0000-0000-000006000000}">
+        <x14:dataValidation type="list" allowBlank="1" showDropDown="1">
           <x14:formula1>
             <xm:f>Lists!$B$24:$B$26</xm:f>
           </x14:formula1>
           <xm:sqref>J2:J500</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showDropDown="1" xr:uid="{00000000-0002-0000-0000-000007000000}">
+        <x14:dataValidation type="list" allowBlank="1" showDropDown="1">
           <x14:formula1>
             <xm:f>Lists!$B$15:$B$18</xm:f>
           </x14:formula1>
           <xm:sqref>K2:K500</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showDropDown="1" xr:uid="{00000000-0002-0000-0000-000008000000}">
+        <x14:dataValidation type="list" allowBlank="1" showDropDown="1">
           <x14:formula1>
             <xm:f>Lists!$B$7:$B$13</xm:f>
           </x14:formula1>
           <xm:sqref>L2:L500</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showDropDown="1" xr:uid="{00000000-0002-0000-0000-000009000000}">
+        <x14:dataValidation type="list" allowBlank="1" showDropDown="1">
           <x14:formula1>
             <xm:f>Lists!$B$43:$B$49</xm:f>
           </x14:formula1>
           <xm:sqref>M2:M500</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showDropDown="1" xr:uid="{00000000-0002-0000-0000-00000A000000}">
+        <x14:dataValidation type="list" allowBlank="1" showDropDown="1">
           <x14:formula1>
             <xm:f>Lists!$B$72:$B$79</xm:f>
           </x14:formula1>
           <xm:sqref>N2:N500</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showDropDown="1" xr:uid="{00000000-0002-0000-0000-00000B000000}">
+        <x14:dataValidation type="list" allowBlank="1" showDropDown="1">
           <x14:formula1>
             <xm:f>Lists!$B$59:$B$63</xm:f>
           </x14:formula1>
           <xm:sqref>P2:P500</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showDropDown="1" xr:uid="{00000000-0002-0000-0000-00000C000000}">
+        <x14:dataValidation type="list" allowBlank="1" showDropDown="1">
           <x14:formula1>
             <xm:f>Lists!$B$51:$B$57</xm:f>
           </x14:formula1>
@@ -5331,9 +5456,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G9"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
@@ -5343,223 +5468,223 @@
     <col min="7" max="7" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>429</v>
+        <v>415</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>430</v>
+        <v>416</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G3" s="2" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="2" t="s">
         <v>432</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="B4" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="D4" s="2" t="s">
         <v>434</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
+      <c r="E4" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>435</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="C2" s="2" t="s">
+      <c r="G4" s="2" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="2" t="s">
         <v>436</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="B5" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>437</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>438</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>439</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>440</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
+      <c r="G5" s="2" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="B6" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>445</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>449</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>451</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>456</v>
-      </c>
       <c r="D6" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>32</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>457</v>
+        <v>443</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" s="2" t="s">
-        <v>458</v>
+        <v>444</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>459</v>
+        <v>445</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>460</v>
+        <v>446</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>439</v>
+        <v>425</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" s="2" t="s">
-        <v>461</v>
+        <v>447</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>61</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>462</v>
+        <v>448</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>463</v>
+        <v>449</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>464</v>
+        <v>450</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>465</v>
+        <v>451</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9" s="2" t="s">
-        <v>466</v>
+        <v>452</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>467</v>
+        <v>453</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>444</v>
+        <v>430</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>439</v>
+        <v>425</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>440</v>
+        <v>426</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G9" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <autoFilter ref="A1:G9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -5567,23 +5692,23 @@
     <col min="4" max="4" width="44" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>468</v>
+        <v>454</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>469</v>
+        <v>455</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="28.8">
       <c r="A2" s="2" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B2" s="2">
         <v>1</v>
@@ -5592,12 +5717,12 @@
         <v>4</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="B3" s="2">
         <v>2</v>
@@ -5606,12 +5731,12 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B4" s="2">
         <v>4</v>
@@ -5620,10 +5745,10 @@
         <v>24</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
         <v>37</v>
       </c>
@@ -5634,117 +5759,117 @@
         <v>72</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>474</v>
+        <v>460</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D5" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <autoFilter ref="A1:D5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B88"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2">
       <c r="A1" s="3" t="s">
-        <v>475</v>
+        <v>461</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="B3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2">
       <c r="B4" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
       <c r="B5" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
       <c r="A7" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
       <c r="B8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2">
       <c r="B9" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2">
       <c r="B10" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
       <c r="B11" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
       <c r="B12" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
       <c r="B13" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
       <c r="A15" s="3" t="s">
         <v>10</v>
       </c>
       <c r="B15" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
       <c r="B16" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
       <c r="B17" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
       <c r="B18" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2">
       <c r="A20" s="3" t="s">
         <v>8</v>
       </c>
@@ -5752,17 +5877,17 @@
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2">
       <c r="B21" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2">
       <c r="B22" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2">
       <c r="A24" s="3" t="s">
         <v>9</v>
       </c>
@@ -5770,17 +5895,17 @@
         <v>36</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2">
       <c r="B25" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2">
       <c r="B26" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2">
       <c r="A28" s="3" t="s">
         <v>4</v>
       </c>
@@ -5788,32 +5913,32 @@
         <v>53</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2">
       <c r="B29" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
       <c r="B30" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
       <c r="B31" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
       <c r="B32" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2">
       <c r="B33" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
       <c r="A35" s="3" t="s">
         <v>5</v>
       </c>
@@ -5821,246 +5946,246 @@
         <v>54</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:2">
       <c r="B36" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
       <c r="B37" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
       <c r="B38" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
       <c r="B39" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:2">
       <c r="B40" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
       <c r="B41" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
       <c r="A43" s="3" t="s">
         <v>12</v>
       </c>
       <c r="B43" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
       <c r="B44" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:2">
       <c r="B45" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
       <c r="B46" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
       <c r="B47" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:2">
       <c r="B48" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
       <c r="B49" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
       <c r="A51" s="3" t="s">
         <v>21</v>
       </c>
       <c r="B51" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
       <c r="B52" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:2">
       <c r="B53" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
       <c r="B54" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
       <c r="B55" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
       <c r="B56" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
       <c r="B57" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
       <c r="A59" s="3" t="s">
         <v>15</v>
       </c>
       <c r="B59" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
       <c r="B60" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:2">
       <c r="B61" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:2">
       <c r="B62" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
       <c r="B63" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
       <c r="A65" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B65" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
       <c r="B66" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
       <c r="B67" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:2">
       <c r="B68" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:2">
       <c r="A71" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:2">
       <c r="B72" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
       <c r="B73" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
       <c r="B74" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
       <c r="B75" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
       <c r="B76" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
       <c r="B77" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
       <c r="B78" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:2">
       <c r="B79" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:2">
       <c r="A81" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:2">
       <c r="B82" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
       <c r="B83" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:2">
       <c r="B84" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
       <c r="B85" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
       <c r="B86" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
       <c r="B87" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:2">
       <c r="B88" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -6069,61 +6194,61 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A13"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="90" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:1" ht="18">
       <c r="A1" s="4" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
       <c r="A3" s="3" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
       <c r="A9" s="3" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>491</v>
+        <v>477</v>
       </c>
     </row>
   </sheetData>
